--- a/daily_eval/Water Collection Sites 2025 V4.xlsx
+++ b/daily_eval/Water Collection Sites 2025 V4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6c86228de80730b2/Genes and Environment/Climate ALS/Climate Justice NC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarah/Satellite_Image_Processing/Bloom_Image_Processing/Blooms/daily_eval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{89C6AF29-1A33-44AE-B482-4A326331D831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F90036-86FC-4410-9C56-B2C988AEC7E7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8BC0ED-27B2-194E-B127-F67619B2C1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{F5A2CA00-80C0-43E4-9700-83B3E09EF1B0}"/>
+    <workbookView xWindow="0" yWindow="7360" windowWidth="28800" windowHeight="17500" xr2:uid="{F5A2CA00-80C0-43E4-9700-83B3E09EF1B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>165 Riverside Dr</t>
   </si>
@@ -63,12 +63,6 @@
     <t>Elizabeth City</t>
   </si>
   <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>lat</t>
-  </si>
-  <si>
     <t>Indian Creek ( Arrowhead Beach)</t>
   </si>
   <si>
@@ -226,6 +220,18 @@
   </si>
   <si>
     <t>Tube Label</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Albemarle Sound</t>
+  </si>
+  <si>
+    <t>CEEG 10</t>
   </si>
 </sst>
 </file>
@@ -307,14 +313,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>412750</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -342,8 +348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="641350" y="3130550"/>
-          <a:ext cx="7340600" cy="3771900"/>
+          <a:off x="704850" y="4203700"/>
+          <a:ext cx="7962900" cy="3898900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -353,10 +359,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -680,56 +682,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B3:N21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="59.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>0</v>
@@ -738,7 +740,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>27944</v>
@@ -750,12 +752,12 @@
         <v>-76.428280000000001</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -764,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>27944</v>
@@ -776,21 +778,21 @@
         <v>-76.332359999999994</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>27921</v>
@@ -802,21 +804,21 @@
         <v>-76.207909999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>27958</v>
@@ -828,18 +830,18 @@
         <v>-76.059399999999997</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
         <v>2</v>
@@ -854,21 +856,21 @@
         <v>-77.002461999999994</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>27924</v>
@@ -881,21 +883,21 @@
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>27932</v>
@@ -907,21 +909,21 @@
         <v>-76.695386999999997</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>27932</v>
@@ -933,12 +935,12 @@
         <v>-76.686425</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -947,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>27932</v>
@@ -959,21 +961,21 @@
         <v>-76.609520000000003</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>27932</v>
@@ -985,21 +987,21 @@
         <v>-76.719210000000004</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
         <v>50</v>
       </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
-      </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>27924</v>
@@ -1011,21 +1013,21 @@
         <v>-76.753900000000002</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>27924</v>
@@ -1037,21 +1039,21 @@
         <v>-76.742630000000005</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>27957</v>
@@ -1063,10 +1065,24 @@
         <v>-76.708444275870605</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17">
+        <v>35.965899999999998</v>
+      </c>
+      <c r="I17">
+        <v>-76.681899999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D21" s="3"/>
     </row>
   </sheetData>
